--- a/SPEC MyBook Pro E1.xlsx
+++ b/SPEC MyBook Pro E1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook PRO\Downloads\Spec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook PRO\Desktop\axioo_b2g\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FC937E-EAE4-4D74-BE85-25D1327518A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DABF82-7F2C-44F8-A058-920BB93D1B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{EC415980-61FC-4EAB-8AD9-40FD9C97A95F}"/>
   </bookViews>
@@ -718,7 +718,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -771,17 +771,6 @@
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -843,6 +832,60 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1131,11 +1174,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1143,43 +1183,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1187,13 +1197,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1210,7 +1220,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1228,7 +1238,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1243,7 +1253,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1279,23 +1289,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1304,7 +1314,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1316,17 +1326,17 @@
     <xf numFmtId="21" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="20" fontId="7" fillId="5" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="17" fillId="4" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="15" fillId="4" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1341,7 +1351,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="7" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1350,7 +1360,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1">
@@ -1377,7 +1387,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="2" applyBorder="1" applyAlignment="1">
@@ -1397,32 +1407,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1442,22 +1428,99 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1839,295 +1902,296 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F7ED28-56AA-4B0E-8F1C-66DBC3E2187D}">
   <dimension ref="A1:D44"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.77734375" style="101" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.109375" style="101" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="101"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="100" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="98" t="s">
+      <c r="A2" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="99" t="s">
+      <c r="B2" s="100" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="103" t="s">
+      <c r="A3" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="103" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="104"/>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="103" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="105" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:4" ht="13.2">
+      <c r="A6" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="108" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="7"/>
+      <c r="D8" s="109"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="100" t="s">
+      <c r="A9" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="105" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="100" t="s">
+      <c r="A10" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="105" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="9"/>
+      <c r="D11" s="112"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="105" t="s">
+      <c r="A12" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="105" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="105"/>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="113"/>
+      <c r="B13" s="105" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="105"/>
-      <c r="B14" s="19" t="s">
+      <c r="A14" s="113"/>
+      <c r="B14" s="114" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="105"/>
-      <c r="B15" s="4" t="s">
+      <c r="A15" s="113"/>
+      <c r="B15" s="105" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="105"/>
-      <c r="B16" s="28" t="s">
+      <c r="A16" s="113"/>
+      <c r="B16" s="111" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="105"/>
-      <c r="B17" s="20" t="s">
+      <c r="A17" s="113"/>
+      <c r="B17" s="115" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="105"/>
-      <c r="B18" s="20" t="s">
+      <c r="A18" s="113"/>
+      <c r="B18" s="115" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="105"/>
-      <c r="B19" s="28" t="s">
+      <c r="A19" s="113"/>
+      <c r="B19" s="111" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="105"/>
-      <c r="B20" s="20" t="s">
+      <c r="A20" s="113"/>
+      <c r="B20" s="115" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="105" t="s">
+      <c r="A21" s="113" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="105" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="105"/>
-      <c r="B22" s="28" t="s">
+      <c r="A22" s="113"/>
+      <c r="B22" s="111" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="113" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="99" t="s">
+      <c r="B23" s="100" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="105"/>
-      <c r="B24" s="28" t="s">
+      <c r="A24" s="113"/>
+      <c r="B24" s="111" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="105" t="s">
+      <c r="A25" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="105" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="105"/>
-      <c r="B26" s="4" t="s">
+      <c r="A26" s="113"/>
+      <c r="B26" s="105" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="105" t="s">
+      <c r="A27" s="113" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="105" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="105"/>
-      <c r="B28" s="4" t="s">
+      <c r="A28" s="113"/>
+      <c r="B28" s="105" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="105" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="116" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15">
-      <c r="A31" s="4" t="s">
+    <row r="31" spans="1:4" ht="13.2">
+      <c r="A31" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="111" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="117"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="105" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="111" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="105" t="s">
+      <c r="A33" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="102" t="s">
+      <c r="B33" s="118" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="105"/>
-      <c r="B34" s="102" t="s">
+      <c r="A34" s="113"/>
+      <c r="B34" s="118" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="12"/>
-      <c r="B35" s="9"/>
+      <c r="A35" s="119"/>
+      <c r="B35" s="112"/>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="12"/>
-      <c r="B36" s="9"/>
+      <c r="A36" s="119"/>
+      <c r="B36" s="112"/>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="12"/>
-      <c r="B37" s="9"/>
+      <c r="A37" s="119"/>
+      <c r="B37" s="112"/>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
+      <c r="A38" s="120"/>
+      <c r="B38" s="121"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
+      <c r="A40" s="122"/>
+      <c r="B40" s="122"/>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
+      <c r="A41" s="122"/>
+      <c r="B41" s="122"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="15"/>
-      <c r="B42" s="16"/>
+      <c r="A42" s="123"/>
+      <c r="B42" s="124"/>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="17"/>
+      <c r="A43" s="125"/>
     </row>
     <row r="44" spans="1:2">
-      <c r="B44" s="14"/>
+      <c r="B44" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2163,1401 +2227,1401 @@
     </row>
     <row r="2" spans="2:7" ht="15" thickBot="1"/>
     <row r="3" spans="2:7" ht="16.2" thickBot="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="112" t="s">
+      <c r="B3" s="87"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="113"/>
-      <c r="F3" s="114"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="95"/>
     </row>
     <row r="4" spans="2:7" ht="15" thickBot="1">
-      <c r="B4" s="108"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="115" t="s">
+      <c r="B4" s="89"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="117"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="98"/>
     </row>
     <row r="5" spans="2:7" ht="15" thickBot="1">
-      <c r="B5" s="108"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="115" t="s">
+      <c r="B5" s="89"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="116"/>
-      <c r="F5" s="117"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="98"/>
     </row>
     <row r="6" spans="2:7" ht="15" thickBot="1">
-      <c r="B6" s="110"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="115" t="s">
+      <c r="B6" s="91"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="96" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="116"/>
-      <c r="F6" s="117"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="98"/>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="10" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="15" thickBot="1">
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="15" thickTop="1">
-      <c r="B10" s="24">
+      <c r="B10" s="13">
         <v>1</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="25"/>
+      <c r="E10" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="14"/>
     </row>
     <row r="11" spans="2:7">
-      <c r="B11" s="26">
+      <c r="B11" s="15">
         <v>2</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="8"/>
+      <c r="E11" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="5"/>
     </row>
     <row r="12" spans="2:7">
-      <c r="B12" s="26">
+      <c r="B12" s="15">
         <v>3</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="8"/>
+      <c r="E12" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" spans="2:7">
-      <c r="B13" s="26">
+      <c r="B13" s="15">
         <v>4</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="8"/>
+      <c r="E13" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="5"/>
     </row>
     <row r="15" spans="2:7">
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="30"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="19"/>
     </row>
     <row r="16" spans="2:7" ht="15" thickBot="1">
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="11" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="15" thickTop="1">
-      <c r="B17" s="24">
+      <c r="B17" s="13">
         <v>1</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="25" t="s">
+      <c r="E17" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="G17" s="24" t="s">
+      <c r="G17" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="24">
+      <c r="B18" s="13">
         <v>2</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" s="25"/>
-      <c r="G18" s="24"/>
+      <c r="E18" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="14"/>
+      <c r="G18" s="13"/>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="24">
+      <c r="B19" s="13">
         <v>3</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="E19" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="8" t="s">
+      <c r="E19" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="G19" s="15" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="24">
+      <c r="B20" s="13">
         <v>4</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D20" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" s="8" t="s">
+      <c r="E20" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="G20" s="15" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="34"/>
-      <c r="G21" s="34"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="23"/>
+      <c r="G21" s="23"/>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="13"/>
+      <c r="E22" s="6"/>
     </row>
     <row r="23" spans="2:7" ht="15" thickBot="1">
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E23" s="36" t="s">
+      <c r="E23" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="11" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="15" thickTop="1">
-      <c r="B24" s="24">
+      <c r="B24" s="13">
         <v>1</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="D24" s="37" t="s">
+      <c r="D24" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="E24" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" s="39"/>
+      <c r="E24" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="28"/>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="26">
+      <c r="B25" s="15">
         <v>2</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="8"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="5"/>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="26">
+      <c r="B26" s="15">
         <v>3</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="F26" s="8"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" s="5"/>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="34"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="17"/>
+      <c r="B27" s="23"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="7"/>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="E28" s="13"/>
+      <c r="E28" s="6"/>
     </row>
     <row r="29" spans="2:7" ht="15" thickBot="1">
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E29" s="36" t="s">
+      <c r="E29" s="25" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="15" thickTop="1">
-      <c r="B30" s="24">
+      <c r="B30" s="13">
         <v>1</v>
       </c>
-      <c r="C30" s="42" t="s">
+      <c r="C30" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="42" t="s">
+      <c r="D30" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="E30" s="43" t="s">
+      <c r="E30" s="32" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="26">
+      <c r="B31" s="15">
         <v>2</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="44" t="s">
+      <c r="B33" s="33" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="34" spans="2:6" ht="15" thickBot="1">
-      <c r="B34" s="45" t="s">
+      <c r="B34" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="C34" s="46" t="s">
+      <c r="C34" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E34" s="46" t="s">
+      <c r="E34" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="F34" s="46" t="s">
+      <c r="F34" s="35" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="35" spans="2:6" ht="15" thickTop="1">
-      <c r="B35" s="43">
+      <c r="B35" s="32">
         <v>1</v>
       </c>
-      <c r="C35" s="42" t="s">
+      <c r="C35" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="D35" s="47" t="s">
+      <c r="D35" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="E35" s="43" t="s">
+      <c r="E35" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="F35" s="43"/>
+      <c r="F35" s="32"/>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="43">
+      <c r="B36" s="32">
         <v>2</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D36" s="47" t="s">
+      <c r="D36" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F36" s="48"/>
+      <c r="E36" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F36" s="37"/>
     </row>
     <row r="37" spans="2:6">
-      <c r="B37" s="43">
+      <c r="B37" s="32">
         <v>3</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F37" s="49"/>
+      <c r="E37" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F37" s="38"/>
     </row>
     <row r="38" spans="2:6">
-      <c r="B38" s="43">
+      <c r="B38" s="32">
         <v>4</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F38" s="49"/>
+      <c r="E38" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F38" s="38"/>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="43">
+      <c r="B39" s="32">
         <v>5</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D39" s="47" t="s">
+      <c r="D39" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F39" s="49"/>
+      <c r="E39" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F39" s="38"/>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="43">
+      <c r="B40" s="32">
         <v>6</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F40" s="49"/>
+      <c r="E40" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F40" s="38"/>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="43">
+      <c r="B41" s="32">
         <v>7</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F41" s="49"/>
+      <c r="E41" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F41" s="38"/>
     </row>
     <row r="42" spans="2:6">
-      <c r="B42" s="43">
+      <c r="B42" s="32">
         <v>8</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F42" s="49"/>
+      <c r="E42" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F42" s="38"/>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="43">
+      <c r="B43" s="32">
         <v>9</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F43" s="49"/>
+      <c r="E43" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F43" s="38"/>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="43">
+      <c r="B44" s="32">
         <v>10</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F44" s="48"/>
+      <c r="E44" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F44" s="37"/>
     </row>
     <row r="45" spans="2:6">
-      <c r="B45" s="43">
+      <c r="B45" s="32">
         <v>11</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F45" s="49"/>
+      <c r="F45" s="38"/>
     </row>
     <row r="46" spans="2:6">
-      <c r="B46" s="43">
+      <c r="B46" s="32">
         <v>12</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F46" s="8"/>
+      <c r="E46" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F46" s="5"/>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="43">
+      <c r="B47" s="32">
         <v>13</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D47" s="50" t="s">
+      <c r="D47" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F47" s="8"/>
+      <c r="E47" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F47" s="5"/>
     </row>
     <row r="48" spans="2:6">
-      <c r="B48" s="43">
+      <c r="B48" s="32">
         <v>16</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D48" s="8"/>
-      <c r="E48" s="2" t="s">
+      <c r="D48" s="5"/>
+      <c r="E48" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F48" s="8"/>
+      <c r="F48" s="5"/>
     </row>
     <row r="49" spans="2:6">
-      <c r="B49" s="2">
+      <c r="B49" s="1">
         <v>17</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D49" s="3"/>
-      <c r="E49" s="2" t="s">
+      <c r="D49" s="2"/>
+      <c r="E49" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F49" s="8"/>
+      <c r="F49" s="5"/>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="2">
+      <c r="B50" s="1">
         <v>18</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D50" s="8"/>
-      <c r="E50" s="2" t="s">
+      <c r="D50" s="5"/>
+      <c r="E50" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F50" s="8"/>
+      <c r="F50" s="5"/>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="2">
+      <c r="B51" s="1">
         <v>19</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="2" t="s">
+      <c r="D51" s="5"/>
+      <c r="E51" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F51" s="8"/>
+      <c r="F51" s="5"/>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="2">
+      <c r="B52" s="1">
         <v>20</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D52" s="47"/>
-      <c r="E52" s="2" t="s">
+      <c r="D52" s="36"/>
+      <c r="E52" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F52" s="8"/>
+      <c r="F52" s="5"/>
     </row>
     <row r="53" spans="2:6">
-      <c r="B53" s="2">
+      <c r="B53" s="1">
         <v>21</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D53" s="47"/>
-      <c r="E53" s="2" t="s">
+      <c r="D53" s="36"/>
+      <c r="E53" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F53" s="8"/>
+      <c r="F53" s="5"/>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="51"/>
-      <c r="C54" s="51"/>
-      <c r="D54" s="52"/>
-      <c r="E54" s="53"/>
-      <c r="F54" s="29"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="42"/>
+      <c r="F54" s="18"/>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="54" t="s">
+      <c r="B55" s="43" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="56" spans="2:6" ht="15" thickBot="1">
-      <c r="B56" s="22" t="s">
+      <c r="B56" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C56" s="22" t="s">
+      <c r="C56" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="D56" s="22" t="s">
+      <c r="D56" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E56" s="22" t="s">
+      <c r="E56" s="11" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="57" spans="2:6" ht="15" thickTop="1">
-      <c r="B57" s="24">
+      <c r="B57" s="13">
         <v>1</v>
       </c>
-      <c r="C57" s="42" t="s">
+      <c r="C57" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="D57" s="55"/>
-      <c r="E57" s="56" t="s">
+      <c r="D57" s="44"/>
+      <c r="E57" s="45" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="58" spans="2:6" ht="13.5" customHeight="1">
-      <c r="B58" s="26">
+      <c r="B58" s="15">
         <v>2</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D58" s="55"/>
-      <c r="E58" s="48" t="s">
+      <c r="D58" s="44"/>
+      <c r="E58" s="37" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="59" spans="2:6">
-      <c r="B59" s="24">
+      <c r="B59" s="13">
         <v>3</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D59" s="55"/>
-      <c r="E59" s="48" t="s">
+      <c r="D59" s="44"/>
+      <c r="E59" s="37" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="60" spans="2:6">
-      <c r="B60" s="24">
+      <c r="B60" s="13">
         <v>4</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D60" s="55"/>
-      <c r="E60" s="48" t="s">
+      <c r="D60" s="44"/>
+      <c r="E60" s="37" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="57"/>
-      <c r="C61" s="58"/>
-      <c r="D61" s="58"/>
-      <c r="E61" s="59"/>
+      <c r="B61" s="46"/>
+      <c r="C61" s="47"/>
+      <c r="D61" s="47"/>
+      <c r="E61" s="48"/>
     </row>
     <row r="62" spans="2:6">
-      <c r="B62" s="60" t="s">
+      <c r="B62" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="C62" s="58"/>
-      <c r="D62" s="58"/>
-      <c r="E62" s="59"/>
+      <c r="C62" s="47"/>
+      <c r="D62" s="47"/>
+      <c r="E62" s="48"/>
     </row>
     <row r="63" spans="2:6" ht="15" thickBot="1">
-      <c r="B63" s="61" t="s">
+      <c r="B63" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="C63" s="61" t="s">
+      <c r="C63" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="D63" s="61" t="s">
+      <c r="D63" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="E63" s="61" t="s">
+      <c r="E63" s="50" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="64" spans="2:6" ht="15.75" customHeight="1" thickTop="1">
-      <c r="B64" s="24">
+      <c r="B64" s="13">
         <v>1</v>
       </c>
-      <c r="C64" s="42" t="s">
+      <c r="C64" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="D64" s="62" t="s">
+      <c r="D64" s="51" t="s">
         <v>140</v>
       </c>
-      <c r="E64" s="56" t="s">
+      <c r="E64" s="45" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="65" spans="2:5" ht="15" customHeight="1">
-      <c r="B65" s="26">
+      <c r="B65" s="15">
         <v>2</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D65" s="63" t="s">
+      <c r="D65" s="52" t="s">
         <v>142</v>
       </c>
-      <c r="E65" s="48" t="s">
+      <c r="E65" s="37" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="15" customHeight="1">
-      <c r="B66" s="26">
+      <c r="B66" s="15">
         <v>3</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D66" s="63" t="s">
+      <c r="D66" s="52" t="s">
         <v>144</v>
       </c>
-      <c r="E66" s="48" t="s">
+      <c r="E66" s="37" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="67" spans="2:5" ht="15" customHeight="1">
-      <c r="B67" s="26">
+      <c r="B67" s="15">
         <v>4</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D67" s="63" t="s">
+      <c r="D67" s="52" t="s">
         <v>146</v>
       </c>
-      <c r="E67" s="48" t="s">
+      <c r="E67" s="37" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="68" spans="2:5" ht="15" customHeight="1">
-      <c r="B68" s="26">
+      <c r="B68" s="15">
         <v>5</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D68" s="63" t="s">
+      <c r="D68" s="52" t="s">
         <v>148</v>
       </c>
-      <c r="E68" s="48" t="s">
+      <c r="E68" s="37" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="69" spans="2:5">
-      <c r="B69" s="34"/>
+      <c r="B69" s="23"/>
     </row>
     <row r="70" spans="2:5">
-      <c r="B70" s="21" t="s">
+      <c r="B70" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="D70" s="64"/>
+      <c r="D70" s="53"/>
     </row>
     <row r="71" spans="2:5" ht="15" thickBot="1">
-      <c r="B71" s="22" t="s">
+      <c r="B71" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C71" s="22" t="s">
+      <c r="C71" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="D71" s="22" t="s">
+      <c r="D71" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="E71" s="22" t="s">
+      <c r="E71" s="11" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="72" spans="2:5" ht="15" thickTop="1">
-      <c r="B72" s="24">
+      <c r="B72" s="13">
         <v>1</v>
       </c>
-      <c r="C72" s="25" t="s">
+      <c r="C72" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="D72" s="65">
+      <c r="D72" s="54">
         <v>579</v>
       </c>
-      <c r="E72" s="25" t="s">
+      <c r="E72" s="14" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="73" spans="2:5">
-      <c r="B73" s="26">
+      <c r="B73" s="15">
         <v>2</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D73" s="66">
+      <c r="D73" s="55">
         <v>73</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E73" s="5" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="74" spans="2:5">
-      <c r="B74" s="26">
+      <c r="B74" s="15">
         <v>3</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D74" s="66">
+      <c r="D74" s="55">
         <v>363</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="5" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="75" spans="2:5">
-      <c r="B75" s="26">
+      <c r="B75" s="15">
         <v>4</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D75" s="66">
+      <c r="D75" s="55">
         <v>122</v>
       </c>
-      <c r="E75" s="8"/>
+      <c r="E75" s="5"/>
     </row>
     <row r="76" spans="2:5">
-      <c r="B76" s="34"/>
-      <c r="D76" s="67"/>
+      <c r="B76" s="23"/>
+      <c r="D76" s="56"/>
     </row>
     <row r="77" spans="2:5">
-      <c r="B77" s="68" t="s">
+      <c r="B77" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="C77" s="69"/>
-      <c r="D77" s="70"/>
-      <c r="E77" s="69"/>
+      <c r="C77" s="58"/>
+      <c r="D77" s="59"/>
+      <c r="E77" s="58"/>
     </row>
     <row r="78" spans="2:5" ht="15" thickBot="1">
-      <c r="B78" s="71" t="s">
+      <c r="B78" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="C78" s="72" t="s">
+      <c r="C78" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="D78" s="72" t="s">
+      <c r="D78" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="E78" s="73" t="s">
+      <c r="E78" s="62" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="79" spans="2:5" ht="15" thickTop="1">
-      <c r="B79" s="74">
+      <c r="B79" s="63">
         <v>1</v>
       </c>
-      <c r="C79" s="75" t="s">
+      <c r="C79" s="64" t="s">
         <v>160</v>
       </c>
-      <c r="D79" s="76" t="s">
+      <c r="D79" s="65" t="s">
         <v>161</v>
       </c>
-      <c r="E79" s="74" t="s">
+      <c r="E79" s="63" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="80" spans="2:5">
-      <c r="B80" s="74">
+      <c r="B80" s="63">
         <v>2</v>
       </c>
-      <c r="C80" s="77" t="s">
+      <c r="C80" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="D80" s="76" t="s">
+      <c r="D80" s="65" t="s">
         <v>163</v>
       </c>
-      <c r="E80" s="74" t="s">
+      <c r="E80" s="63" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="74">
+      <c r="B81" s="63">
         <v>3</v>
       </c>
-      <c r="C81" s="75" t="s">
+      <c r="C81" s="64" t="s">
         <v>164</v>
       </c>
-      <c r="D81" s="76" t="s">
+      <c r="D81" s="65" t="s">
         <v>165</v>
       </c>
-      <c r="E81" s="74" t="s">
+      <c r="E81" s="63" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="82" spans="2:6">
-      <c r="B82" s="74">
+      <c r="B82" s="63">
         <v>5</v>
       </c>
-      <c r="C82" s="77" t="s">
+      <c r="C82" s="66" t="s">
         <v>166</v>
       </c>
-      <c r="D82" s="76" t="s">
+      <c r="D82" s="65" t="s">
         <v>167</v>
       </c>
-      <c r="E82" s="74" t="s">
+      <c r="E82" s="63" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="83" spans="2:6">
-      <c r="B83" s="74">
+      <c r="B83" s="63">
         <v>6</v>
       </c>
-      <c r="C83" s="78" t="s">
+      <c r="C83" s="67" t="s">
         <v>168</v>
       </c>
-      <c r="D83" s="76" t="s">
+      <c r="D83" s="65" t="s">
         <v>169</v>
       </c>
-      <c r="E83" s="79" t="s">
+      <c r="E83" s="68" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="84" spans="2:6">
-      <c r="B84" s="34"/>
-      <c r="C84" s="80"/>
-      <c r="D84" s="81"/>
-      <c r="E84" s="82"/>
+      <c r="B84" s="23"/>
+      <c r="C84" s="69"/>
+      <c r="D84" s="70"/>
+      <c r="E84" s="71"/>
     </row>
     <row r="85" spans="2:6">
-      <c r="B85" s="83" t="s">
+      <c r="B85" s="72" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="86" spans="2:6">
-      <c r="B86" s="84" t="s">
+      <c r="B86" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="C86" s="85" t="s">
+      <c r="C86" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="D86" s="85" t="s">
+      <c r="D86" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="E86" s="85" t="s">
+      <c r="E86" s="74" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="87" spans="2:6">
-      <c r="B87" s="26">
+      <c r="B87" s="15">
         <v>1</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D87" s="32"/>
-      <c r="E87" s="26" t="s">
+      <c r="D87" s="21"/>
+      <c r="E87" s="15" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="88" spans="2:6">
-      <c r="B88" s="26">
+      <c r="B88" s="15">
         <v>2</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D88" s="26"/>
-      <c r="E88" s="26" t="s">
+      <c r="D88" s="15"/>
+      <c r="E88" s="15" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="89" spans="2:6">
-      <c r="B89" s="26">
+      <c r="B89" s="15">
         <v>3</v>
       </c>
-      <c r="C89" s="19" t="s">
+      <c r="C89" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D89" s="32"/>
-      <c r="E89" s="26" t="s">
+      <c r="D89" s="21"/>
+      <c r="E89" s="15" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="90" spans="2:6">
-      <c r="B90" s="26">
+      <c r="B90" s="15">
         <v>4</v>
       </c>
-      <c r="C90" s="19" t="s">
+      <c r="C90" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D90" s="26"/>
-      <c r="E90" s="26" t="s">
+      <c r="D90" s="15"/>
+      <c r="E90" s="15" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="91" spans="2:6">
-      <c r="B91" s="26">
+      <c r="B91" s="15">
         <v>5</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D91" s="26"/>
-      <c r="E91" s="26" t="s">
+      <c r="D91" s="15"/>
+      <c r="E91" s="15" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="92" spans="2:6">
-      <c r="B92" s="26">
+      <c r="B92" s="15">
         <v>6</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D92" s="26"/>
-      <c r="E92" s="26" t="s">
+      <c r="D92" s="15"/>
+      <c r="E92" s="15" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="93" spans="2:6">
-      <c r="B93" s="26">
+      <c r="B93" s="15">
         <v>7</v>
       </c>
-      <c r="C93" s="20" t="s">
+      <c r="C93" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D93" s="26"/>
-      <c r="E93" s="26" t="s">
+      <c r="D93" s="15"/>
+      <c r="E93" s="15" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="94" spans="2:6">
-      <c r="B94" s="34"/>
-      <c r="D94" s="34"/>
-      <c r="E94" s="34"/>
+      <c r="B94" s="23"/>
+      <c r="D94" s="23"/>
+      <c r="E94" s="23"/>
     </row>
     <row r="95" spans="2:6">
-      <c r="B95" s="83" t="s">
+      <c r="B95" s="72" t="s">
         <v>174</v>
       </c>
-      <c r="C95" s="86"/>
-      <c r="D95" s="34"/>
-      <c r="E95" s="34"/>
+      <c r="C95" s="75"/>
+      <c r="D95" s="23"/>
+      <c r="E95" s="23"/>
     </row>
     <row r="96" spans="2:6" ht="15" thickBot="1">
-      <c r="B96" s="87" t="s">
+      <c r="B96" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="C96" s="73" t="s">
+      <c r="C96" s="62" t="s">
         <v>175</v>
       </c>
-      <c r="D96" s="87" t="s">
+      <c r="D96" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="E96" s="87" t="s">
+      <c r="E96" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="F96" s="87" t="s">
+      <c r="F96" s="76" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="97" spans="2:6" ht="15" thickTop="1">
-      <c r="B97" s="24">
+      <c r="B97" s="13">
         <v>1</v>
       </c>
-      <c r="C97" s="88" t="s">
+      <c r="C97" s="77" t="s">
         <v>177</v>
       </c>
-      <c r="D97" s="31" t="s">
+      <c r="D97" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="E97" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="F97" s="24"/>
+      <c r="E97" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F97" s="13"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="26">
+      <c r="B98" s="15">
         <v>2</v>
       </c>
-      <c r="C98" s="28" t="s">
+      <c r="C98" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="D98" s="32" t="s">
+      <c r="D98" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="E98" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="F98" s="26"/>
+      <c r="E98" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F98" s="15"/>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="26">
+      <c r="B99" s="15">
         <v>3</v>
       </c>
-      <c r="C99" s="28" t="s">
+      <c r="C99" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="D99" s="32" t="s">
+      <c r="D99" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="E99" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="F99" s="26"/>
+      <c r="E99" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F99" s="15"/>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="34"/>
-      <c r="C100" s="86"/>
-      <c r="D100" s="34"/>
-      <c r="E100" s="34"/>
+      <c r="B100" s="23"/>
+      <c r="C100" s="75"/>
+      <c r="D100" s="23"/>
+      <c r="E100" s="23"/>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="68" t="s">
+      <c r="B101" s="57" t="s">
         <v>183</v>
       </c>
-      <c r="C101" s="69"/>
-      <c r="D101" s="69"/>
-      <c r="E101" s="81"/>
+      <c r="C101" s="58"/>
+      <c r="D101" s="58"/>
+      <c r="E101" s="70"/>
     </row>
     <row r="102" spans="2:6" ht="15" thickBot="1">
-      <c r="B102" s="71" t="s">
+      <c r="B102" s="60" t="s">
         <v>184</v>
       </c>
-      <c r="C102" s="89" t="s">
+      <c r="C102" s="78" t="s">
         <v>185</v>
       </c>
-      <c r="D102" s="71" t="s">
+      <c r="D102" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="E102" s="71" t="s">
+      <c r="E102" s="60" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="103" spans="2:6" ht="15" thickTop="1">
-      <c r="B103" s="74">
+      <c r="B103" s="63">
         <v>1</v>
       </c>
-      <c r="C103" s="90"/>
-      <c r="D103" s="91" t="s">
+      <c r="C103" s="79"/>
+      <c r="D103" s="80" t="s">
         <v>187</v>
       </c>
-      <c r="E103" s="26">
+      <c r="E103" s="15">
         <v>311.60000000000002</v>
       </c>
     </row>
     <row r="104" spans="2:6">
-      <c r="B104" s="92">
+      <c r="B104" s="81">
         <v>2</v>
       </c>
-      <c r="C104" s="93"/>
-      <c r="D104" s="94" t="s">
+      <c r="C104" s="82"/>
+      <c r="D104" s="83" t="s">
         <v>188</v>
       </c>
-      <c r="E104" s="26">
+      <c r="E104" s="15">
         <v>217.8</v>
       </c>
     </row>
     <row r="105" spans="2:6">
-      <c r="B105" s="92">
+      <c r="B105" s="81">
         <v>3</v>
       </c>
-      <c r="C105" s="95"/>
-      <c r="D105" s="94" t="s">
+      <c r="C105" s="84"/>
+      <c r="D105" s="83" t="s">
         <v>189</v>
       </c>
-      <c r="E105" s="26">
+      <c r="E105" s="15">
         <v>17.3</v>
       </c>
     </row>
     <row r="106" spans="2:6">
-      <c r="B106" s="81"/>
-      <c r="C106" s="69"/>
-      <c r="D106" s="69"/>
-      <c r="E106" s="81"/>
+      <c r="B106" s="70"/>
+      <c r="C106" s="58"/>
+      <c r="D106" s="58"/>
+      <c r="E106" s="70"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="68" t="s">
+      <c r="B107" s="57" t="s">
         <v>183</v>
       </c>
-      <c r="C107" s="69"/>
-      <c r="D107" s="69"/>
-      <c r="E107" s="81"/>
+      <c r="C107" s="58"/>
+      <c r="D107" s="58"/>
+      <c r="E107" s="70"/>
     </row>
     <row r="108" spans="2:6" ht="15" thickBot="1">
-      <c r="B108" s="71" t="s">
+      <c r="B108" s="60" t="s">
         <v>184</v>
       </c>
-      <c r="C108" s="71" t="s">
+      <c r="C108" s="60" t="s">
         <v>185</v>
       </c>
-      <c r="D108" s="71" t="s">
+      <c r="D108" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="E108" s="71" t="s">
+      <c r="E108" s="60" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="109" spans="2:6" ht="15" thickTop="1">
-      <c r="B109" s="74">
+      <c r="B109" s="63">
         <v>1</v>
       </c>
-      <c r="C109" s="91" t="s">
+      <c r="C109" s="80" t="s">
         <v>191</v>
       </c>
-      <c r="D109" s="91" t="s">
+      <c r="D109" s="80" t="s">
         <v>192</v>
       </c>
-      <c r="E109" s="26">
+      <c r="E109" s="15">
         <v>1.34</v>
       </c>
     </row>
     <row r="110" spans="2:6">
-      <c r="B110" s="74">
+      <c r="B110" s="63">
         <v>2</v>
       </c>
-      <c r="C110" s="94" t="s">
+      <c r="C110" s="83" t="s">
         <v>193</v>
       </c>
-      <c r="D110" s="94"/>
-      <c r="E110" s="26">
+      <c r="D110" s="83"/>
+      <c r="E110" s="15">
         <v>0.2</v>
       </c>
     </row>
     <row r="111" spans="2:6">
-      <c r="B111" s="74">
+      <c r="B111" s="63">
         <v>3</v>
       </c>
-      <c r="C111" s="94" t="s">
+      <c r="C111" s="83" t="s">
         <v>194</v>
       </c>
-      <c r="D111" s="94"/>
-      <c r="E111" s="26">
+      <c r="D111" s="83"/>
+      <c r="E111" s="15">
         <f>SUM(E109:E110)</f>
         <v>1.54</v>
       </c>
     </row>
     <row r="112" spans="2:6">
-      <c r="B112" s="81"/>
-      <c r="C112" s="69"/>
-      <c r="D112" s="69"/>
-      <c r="E112" s="34"/>
+      <c r="B112" s="70"/>
+      <c r="C112" s="58"/>
+      <c r="D112" s="58"/>
+      <c r="E112" s="23"/>
     </row>
     <row r="113" spans="2:5">
-      <c r="B113" s="68" t="s">
+      <c r="B113" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="C113" s="69"/>
-      <c r="D113" s="69"/>
-      <c r="E113" s="81"/>
+      <c r="C113" s="58"/>
+      <c r="D113" s="58"/>
+      <c r="E113" s="70"/>
     </row>
     <row r="114" spans="2:5" ht="15" thickBot="1">
-      <c r="B114" s="71" t="s">
+      <c r="B114" s="60" t="s">
         <v>184</v>
       </c>
-      <c r="C114" s="71" t="s">
+      <c r="C114" s="60" t="s">
         <v>195</v>
       </c>
-      <c r="D114" s="71" t="s">
+      <c r="D114" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="E114" s="71" t="s">
+      <c r="E114" s="60" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="115" spans="2:5" ht="15" thickTop="1">
-      <c r="B115" s="74">
+      <c r="B115" s="63">
         <v>1</v>
       </c>
-      <c r="C115" s="91" t="s">
+      <c r="C115" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="D115" s="91"/>
-      <c r="E115" s="74" t="s">
+      <c r="D115" s="80"/>
+      <c r="E115" s="63" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="116" spans="2:5">
-      <c r="B116" s="74">
+      <c r="B116" s="63">
         <v>2</v>
       </c>
-      <c r="C116" s="94" t="s">
+      <c r="C116" s="83" t="s">
         <v>197</v>
       </c>
-      <c r="D116" s="94"/>
-      <c r="E116" s="74" t="s">
+      <c r="D116" s="83"/>
+      <c r="E116" s="63" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="118" spans="2:5">
-      <c r="B118" s="96" t="s">
+      <c r="B118" s="85" t="s">
         <v>199</v>
       </c>
-      <c r="E118" s="96" t="s">
+      <c r="E118" s="85" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="119" spans="2:5">
-      <c r="B119" s="96"/>
-      <c r="E119" s="96"/>
+      <c r="B119" s="85"/>
+      <c r="E119" s="85"/>
     </row>
     <row r="120" spans="2:5">
-      <c r="B120" s="96"/>
-      <c r="E120" s="96"/>
+      <c r="B120" s="85"/>
+      <c r="E120" s="85"/>
     </row>
     <row r="121" spans="2:5">
-      <c r="B121" s="96"/>
-      <c r="E121" s="96"/>
+      <c r="B121" s="85"/>
+      <c r="E121" s="85"/>
     </row>
     <row r="122" spans="2:5">
-      <c r="B122" s="96"/>
-      <c r="E122" s="96"/>
+      <c r="B122" s="85"/>
+      <c r="E122" s="85"/>
     </row>
     <row r="123" spans="2:5">
-      <c r="B123" s="97" t="s">
+      <c r="B123" s="86" t="s">
         <v>201</v>
       </c>
-      <c r="E123" s="97" t="s">
+      <c r="E123" s="86" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="124" spans="2:5">
-      <c r="B124" s="96" t="s">
+      <c r="B124" s="85" t="s">
         <v>202</v>
       </c>
-      <c r="E124" s="96" t="s">
+      <c r="E124" s="85" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="141" spans="3:3">
-      <c r="C141" s="26"/>
+      <c r="C141" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3574,26 +3638,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="189b1353-a086-487c-981c-f6344e352306" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82bd302-08e5-41cf-ac7e-929bc680f927">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007F1C94A586F6A64AA956C7CA2AB05C9B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f4315622f99eaf65af18b57ec807dec5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f82bd302-08e5-41cf-ac7e-929bc680f927" xmlns:ns3="189b1353-a086-487c-981c-f6344e352306" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce1289053e2708c538c907a002d6effc" ns2:_="" ns3:_="">
     <xsd:import namespace="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
@@ -3828,10 +3872,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="189b1353-a086-487c-981c-f6344e352306" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82bd302-08e5-41cf-ac7e-929bc680f927">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F9D72A0-B605-4CD1-A771-1D9B594C54D3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACFAC14E-D454-4E2E-8CDB-2C64EC919C08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
+    <ds:schemaRef ds:uri="189b1353-a086-487c-981c-f6344e352306"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3848,20 +3923,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACFAC14E-D454-4E2E-8CDB-2C64EC919C08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F9D72A0-B605-4CD1-A771-1D9B594C54D3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f82bd302-08e5-41cf-ac7e-929bc680f927"/>
-    <ds:schemaRef ds:uri="189b1353-a086-487c-981c-f6344e352306"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>